--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75FDABF4-ED35-446B-8F7D-00575317D96F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{316AF044-1F0E-48B7-829B-AD654F6E4753}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{D89C3952-A4D5-4122-BF94-E2D5C52585CA}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="16">
   <si>
     <t>분류</t>
   </si>
@@ -76,6 +76,14 @@
   </si>
   <si>
     <t>현행</t>
+  </si>
+  <si>
+    <t>파일명</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>규정관리규정.txt</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -439,7 +447,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9B87EBAC-A982-4D2C-9CDB-54EB818C0DB3}">
-  <dimension ref="A1:E4"/>
+  <dimension ref="A1:F4"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="6.125" bestFit="1" customWidth="1"/>
@@ -447,9 +455,10 @@
     <col min="3" max="3" width="7" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="12.125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="5" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15.875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -465,8 +474,11 @@
       <c r="E1" t="s">
         <v>4</v>
       </c>
+      <c r="F1" t="s">
+        <v>14</v>
+      </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -480,7 +492,7 @@
         <v>45292</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>8</v>
       </c>
@@ -493,8 +505,11 @@
       <c r="D3">
         <v>45275</v>
       </c>
+      <c r="F3" t="s">
+        <v>15</v>
+      </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>10</v>
       </c>
